--- a/readlark-top-100-books.xlsx
+++ b/readlark-top-100-books.xlsx
@@ -492,7 +492,7 @@
           <t>Launch Order</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
@@ -569,7 +569,7 @@
       <c r="H6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -821,6 +821,11 @@
       </c>
       <c r="H13" s="11" t="n">
         <v>2</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4906,7 +4911,7 @@
           <t>Why this slot</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>Video</t>
         </is>
@@ -4931,7 +4936,7 @@
           <t>Anchor — flagship launch video (already live); biggest habits search term</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -4954,6 +4959,11 @@
       <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Anchor — top modern money title; broad appeal</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/readlark-top-100-books.xlsx
+++ b/readlark-top-100-books.xlsx
@@ -822,7 +822,7 @@
       <c r="H13" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
@@ -4961,7 +4961,7 @@
           <t>Anchor — top modern money title; broad appeal</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>

--- a/readlark-top-100-books.xlsx
+++ b/readlark-top-100-books.xlsx
@@ -1246,6 +1246,11 @@
       </c>
       <c r="H25" s="11" t="n">
         <v>3</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="16">
@@ -4984,6 +4989,11 @@
       <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Rankable — strong demand, lighter competition than the anchors</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/readlark-top-100-books.xlsx
+++ b/readlark-top-100-books.xlsx
@@ -786,6 +786,11 @@
       <c r="H12" s="11" t="n">
         <v>4</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1247,7 +1252,7 @@
       <c r="H25" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
@@ -4991,7 +4996,7 @@
           <t>Rankable — strong demand, lighter competition than the anchors</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
@@ -5014,6 +5019,11 @@
       <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Anchor classic — evergreen search floor</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
